--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -4965,7 +4965,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, admin@admin.com</t>
+          <t>admin@admin.com, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, admin@admin.com</t>
+          <t>admin@admin.com, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, admin@admin.com</t>
+          <t>admin@admin.com, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>system, backup@backdoor.com, System</t>
+          <t>System, system, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, System</t>
+          <t>System, admin@admin.com</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>system, backup@backdoor.com, System</t>
+          <t>System, system, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, System</t>
+          <t>System, admin@admin.com</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>system, backup@backdoor.com, System</t>
+          <t>System, system, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, System</t>
+          <t>System, admin@admin.com</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>System, admin@admin.com</t>
+          <t>admin@admin.com, System</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>System, admin@admin.com</t>
+          <t>admin@admin.com, System</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>System, admin@admin.com</t>
+          <t>admin@admin.com, System</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>System, system, backup@backdoor.com</t>
+          <t>System, backup@backdoor.com, system</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, System</t>
+          <t>System, admin@admin.com</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>System, system, backup@backdoor.com</t>
+          <t>System, backup@backdoor.com, system</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, System</t>
+          <t>System, admin@admin.com</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>System, system, backup@backdoor.com</t>
+          <t>System, backup@backdoor.com, system</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, System</t>
+          <t>System, admin@admin.com</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, admin@admin.com</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, admin@admin.com</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, admin@admin.com</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com, system</t>
+          <t>system, System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>System, admin@admin.com</t>
+          <t>admin@admin.com, System</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com, system</t>
+          <t>system, System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>System, admin@admin.com</t>
+          <t>admin@admin.com, System</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com, system</t>
+          <t>system, System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>System, admin@admin.com</t>
+          <t>admin@admin.com, System</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, admin@admin.com</t>
+          <t>admin@admin.com, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, admin@admin.com</t>
+          <t>admin@admin.com, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, admin@admin.com</t>
+          <t>admin@admin.com, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>system, System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, system, System</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>system, System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, system, System</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>system, System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, system, System</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, admin@admin.com</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, admin@admin.com</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, admin@admin.com</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, system, System</t>
+          <t>system, System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, System</t>
+          <t>System, admin@admin.com</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, system, System</t>
+          <t>system, System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, System</t>
+          <t>System, admin@admin.com</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, system, System</t>
+          <t>system, System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, System</t>
+          <t>System, admin@admin.com</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, admin@admin.com</t>
+          <t>admin@admin.com, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, admin@admin.com</t>
+          <t>admin@admin.com, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, admin@admin.com</t>
+          <t>admin@admin.com, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>system, System, backup@backdoor.com</t>
+          <t>system, backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>System, admin@admin.com</t>
+          <t>admin@admin.com, System</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>system, System, backup@backdoor.com</t>
+          <t>system, backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>System, admin@admin.com</t>
+          <t>admin@admin.com, System</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>system, System, backup@backdoor.com</t>
+          <t>system, backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>System, admin@admin.com</t>
+          <t>admin@admin.com, System</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>system, backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com, system</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, System</t>
+          <t>System, admin@admin.com</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>system, backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com, system</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, System</t>
+          <t>System, admin@admin.com</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>system, backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com, system</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, System</t>
+          <t>System, admin@admin.com</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, admin@admin.com</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, admin@admin.com</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, admin@admin.com</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com, system</t>
+          <t>backup@backdoor.com, System, system</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com, system</t>
+          <t>backup@backdoor.com, System, system</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com, system</t>
+          <t>backup@backdoor.com, System, system</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System, system</t>
+          <t>System, backup@backdoor.com, system</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System, system</t>
+          <t>System, backup@backdoor.com, system</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System, system</t>
+          <t>System, backup@backdoor.com, system</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com, system</t>
+          <t>system, System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com, system</t>
+          <t>system, System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com, system</t>
+          <t>system, System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>system, System, backup@backdoor.com</t>
+          <t>System, backup@backdoor.com, system</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>System, admin@admin.com</t>
+          <t>admin@admin.com, System</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>system, System, backup@backdoor.com</t>
+          <t>System, backup@backdoor.com, system</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>System, admin@admin.com</t>
+          <t>admin@admin.com, System</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>system, System, backup@backdoor.com</t>
+          <t>System, backup@backdoor.com, system</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>System, admin@admin.com</t>
+          <t>admin@admin.com, System</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, admin@admin.com</t>
+          <t>admin@admin.com, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, admin@admin.com</t>
+          <t>admin@admin.com, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, admin@admin.com</t>
+          <t>admin@admin.com, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com, system</t>
+          <t>backup@backdoor.com, System, system</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com, system</t>
+          <t>backup@backdoor.com, System, system</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com, system</t>
+          <t>backup@backdoor.com, System, system</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System, system</t>
+          <t>System, backup@backdoor.com, system</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, System</t>
+          <t>System, admin@admin.com</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System, system</t>
+          <t>System, backup@backdoor.com, system</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, System</t>
+          <t>System, admin@admin.com</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System, system</t>
+          <t>System, backup@backdoor.com, system</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, System</t>
+          <t>System, admin@admin.com</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, admin@admin.com</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, admin@admin.com</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, admin@admin.com</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com, system</t>
+          <t>system, backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>System, admin@admin.com</t>
+          <t>admin@admin.com, System</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com, system</t>
+          <t>system, backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>System, admin@admin.com</t>
+          <t>admin@admin.com, System</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com, system</t>
+          <t>system, backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>System, admin@admin.com</t>
+          <t>admin@admin.com, System</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>system, backup@backdoor.com, System</t>
+          <t>System, system, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>system, backup@backdoor.com, System</t>
+          <t>System, system, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>system, backup@backdoor.com, System</t>
+          <t>System, system, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, admin@admin.com</t>
+          <t>admin@admin.com, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, admin@admin.com</t>
+          <t>admin@admin.com, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, admin@admin.com</t>
+          <t>admin@admin.com, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>System, system, backup@backdoor.com</t>
+          <t>system, backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>System, system, backup@backdoor.com</t>
+          <t>system, backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>System, system, backup@backdoor.com</t>
+          <t>system, backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, admin@admin.com</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, admin@admin.com</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, admin@admin.com</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>system, backup@backdoor.com, System</t>
+          <t>system, System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, System</t>
+          <t>System, admin@admin.com</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>system, backup@backdoor.com, System</t>
+          <t>system, System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, System</t>
+          <t>System, admin@admin.com</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>system, backup@backdoor.com, System</t>
+          <t>system, System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, System</t>
+          <t>System, admin@admin.com</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>System, admin@admin.com</t>
+          <t>admin@admin.com, System</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>System, admin@admin.com</t>
+          <t>admin@admin.com, System</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>System, admin@admin.com</t>
+          <t>admin@admin.com, System</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, admin@admin.com</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, admin@admin.com</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, admin@admin.com</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>system, System, backup@backdoor.com</t>
+          <t>System, backup@backdoor.com, system</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, System</t>
+          <t>System, admin@admin.com</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>system, System, backup@backdoor.com</t>
+          <t>System, backup@backdoor.com, system</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, System</t>
+          <t>System, admin@admin.com</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>system, System, backup@backdoor.com</t>
+          <t>System, backup@backdoor.com, system</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, System</t>
+          <t>System, admin@admin.com</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com, system</t>
+          <t>backup@backdoor.com, System, system</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com, system</t>
+          <t>backup@backdoor.com, System, system</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com, system</t>
+          <t>backup@backdoor.com, System, system</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System, system</t>
+          <t>system, backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System, system</t>
+          <t>system, backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System, system</t>
+          <t>system, backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, admin@admin.com</t>
+          <t>admin@admin.com, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, admin@admin.com</t>
+          <t>admin@admin.com, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, admin@admin.com</t>
+          <t>admin@admin.com, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>system, backup@backdoor.com, System</t>
+          <t>system, System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>System, admin@admin.com</t>
+          <t>admin@admin.com, System</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>system, backup@backdoor.com, System</t>
+          <t>system, System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>System, admin@admin.com</t>
+          <t>admin@admin.com, System</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>system, backup@backdoor.com, System</t>
+          <t>system, System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>System, admin@admin.com</t>
+          <t>admin@admin.com, System</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System</t>
+          <t>System, backup@backdoor.com</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>system, System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, system, System</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>system, System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, system, System</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>system, System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, system, System</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>System, backup@backdoor.com</t>
+          <t>backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, system, System</t>
+          <t>backup@backdoor.com, System, system</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, System</t>
+          <t>System, admin@admin.com</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, system, System</t>
+          <t>backup@backdoor.com, System, system</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, System</t>
+          <t>System, admin@admin.com</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, system, System</t>
+          <t>backup@backdoor.com, System, system</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, System</t>
+          <t>System, admin@admin.com</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, admin@admin.com</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, admin@admin.com</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>admin@admin.com, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, admin@admin.com</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System, system</t>
+          <t>system, backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>System, admin@admin.com</t>
+          <t>admin@admin.com, System</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System, system</t>
+          <t>system, backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>System, admin@admin.com</t>
+          <t>admin@admin.com, System</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>backup@backdoor.com, System, system</t>
+          <t>system, backup@backdoor.com, System</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>System, admin@admin.com</t>
+          <t>admin@admin.com, System</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -52,14 +52,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0090EE90"/>
-        <bgColor rgb="0090EE90"/>
+        <fgColor rgb="00FFB6C1"/>
+        <bgColor rgb="00FFB6C1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFB6C1"/>
-        <bgColor rgb="00FFB6C1"/>
+        <fgColor rgb="0090EE90"/>
+        <bgColor rgb="0090EE90"/>
       </patternFill>
     </fill>
     <fill>
@@ -93,10 +93,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -476,9 +476,9 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="37" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
@@ -568,19 +568,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>system, backup@backdoor.com, System</t>
-        </is>
-      </c>
+      <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>33/52</t>
+          <t>0/52</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -620,19 +616,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>52/52</t>
+          <t>0/52</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
@@ -677,19 +669,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>backup@backdoor.com, System</t>
-        </is>
-      </c>
+      <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42/52</t>
+          <t>0/52</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
@@ -732,19 +720,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>backup@backdoor.com, System</t>
-        </is>
-      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35/52</t>
+          <t>0/52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -787,19 +771,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>45/52</t>
+          <t>0/52</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
@@ -808,7 +788,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -842,19 +822,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>admin@admin.com, System</t>
-        </is>
-      </c>
+      <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35/52</t>
+          <t>0/52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -863,7 +839,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8">
@@ -897,19 +873,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>backup@backdoor.com, System</t>
-        </is>
-      </c>
+      <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44/52</t>
+          <t>0/52</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
@@ -952,19 +924,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21/52</t>
+          <t>0/52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -974,7 +942,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1009,19 +977,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27/52</t>
+          <t>0/52</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
@@ -1031,7 +995,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1066,19 +1030,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34/52</t>
+          <t>0/52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -1113,19 +1073,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31/52</t>
+          <t>0/52</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -1160,19 +1116,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36/52</t>
+          <t>0/52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -1212,19 +1164,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36/52</t>
+          <t>0/52</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K14" s="1" t="inlineStr">
@@ -1304,19 +1252,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>43/52</t>
+          <t>0/52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
@@ -1336,22 +1280,22 @@
         <v>26</v>
       </c>
       <c r="O15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="4" t="n">
         <v>26</v>
-      </c>
-      <c r="P15" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1386,19 +1330,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42/52</t>
+          <t>0/52</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
@@ -1418,22 +1358,22 @@
         <v>26</v>
       </c>
       <c r="O16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="4" t="n">
         <v>26</v>
-      </c>
-      <c r="P16" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1468,19 +1408,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36/52</t>
+          <t>0/52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -1500,22 +1436,22 @@
         <v>26</v>
       </c>
       <c r="O17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="4" t="n">
         <v>26</v>
-      </c>
-      <c r="P17" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1550,19 +1486,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38/52</t>
+          <t>0/52</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
@@ -1582,22 +1514,22 @@
         <v>26</v>
       </c>
       <c r="O18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="4" t="n">
         <v>26</v>
-      </c>
-      <c r="P18" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1632,19 +1564,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35/52</t>
+          <t>0/52</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
@@ -1664,22 +1592,22 @@
         <v>26</v>
       </c>
       <c r="O19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="4" t="n">
         <v>26</v>
-      </c>
-      <c r="P19" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1714,19 +1642,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42/52</t>
+          <t>0/52</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
@@ -1746,22 +1670,22 @@
         <v>26</v>
       </c>
       <c r="O20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="4" t="n">
         <v>26</v>
-      </c>
-      <c r="P20" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1796,19 +1720,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>42/52</t>
+          <t>0/52</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -1843,19 +1763,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31/52</t>
+          <t>0/52</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -1890,19 +1806,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>System</t>
-        </is>
-      </c>
+      <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>41/52</t>
+          <t>0/52</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -1942,19 +1854,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27/52</t>
+          <t>0/52</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K24" s="1" t="inlineStr">
@@ -2004,19 +1912,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26/52</t>
+          <t>0/52</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -2066,19 +1970,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32/52</t>
+          <t>0/52</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
@@ -2128,19 +2028,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14/52</t>
+          <t>0/52</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
@@ -2190,19 +2086,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>system, backup@backdoor.com, System</t>
-        </is>
-      </c>
+      <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>36/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -2237,19 +2129,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>42/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -2284,19 +2172,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>backup@backdoor.com, System</t>
-        </is>
-      </c>
+      <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>56/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -2331,19 +2215,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>backup@backdoor.com, System</t>
-        </is>
-      </c>
+      <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>38/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -2378,19 +2258,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>43/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -2425,19 +2301,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>admin@admin.com, System</t>
-        </is>
-      </c>
+      <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>31/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -2472,19 +2344,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>backup@backdoor.com, System</t>
-        </is>
-      </c>
+      <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>41/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -2519,19 +2387,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>27/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -2566,19 +2430,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>20/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -2613,19 +2473,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>33/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -2660,19 +2516,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>37/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -2707,19 +2559,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>36/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -2754,19 +2602,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>45/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -2801,19 +2645,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>46/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -2848,19 +2688,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>44/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -2895,19 +2731,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>43/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -2942,19 +2774,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>39/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -2989,19 +2817,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>39/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3036,19 +2860,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>32/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3083,19 +2903,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>41/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3130,19 +2946,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>33/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3177,19 +2989,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>System</t>
-        </is>
-      </c>
+      <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>41/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3224,19 +3032,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>41/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3271,19 +3075,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>27/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3318,19 +3118,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>34/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3365,19 +3161,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>12/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3412,19 +3204,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>system, backup@backdoor.com, System</t>
-        </is>
-      </c>
+      <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>55/55</t>
+          <t>0/55</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3459,19 +3247,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>29/55</t>
+          <t>0/55</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3506,19 +3290,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>backup@backdoor.com, System</t>
-        </is>
-      </c>
+      <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>31/55</t>
+          <t>0/55</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3553,19 +3333,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>backup@backdoor.com, System</t>
-        </is>
-      </c>
+      <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>31/55</t>
+          <t>0/55</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3600,19 +3376,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>37/55</t>
+          <t>0/55</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3647,19 +3419,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>admin@admin.com, System</t>
-        </is>
-      </c>
+      <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>40/55</t>
+          <t>0/55</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3694,19 +3462,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>backup@backdoor.com, System</t>
-        </is>
-      </c>
+      <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>34/55</t>
+          <t>0/55</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3741,19 +3505,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>29/55</t>
+          <t>0/55</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3788,19 +3548,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>29/55</t>
+          <t>0/55</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3835,19 +3591,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>30/55</t>
+          <t>0/55</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3882,19 +3634,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>23/55</t>
+          <t>0/55</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3929,19 +3677,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>37/55</t>
+          <t>0/55</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3976,19 +3720,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>39/55</t>
+          <t>0/55</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4023,19 +3763,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>37/55</t>
+          <t>0/55</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4070,19 +3806,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>36/55</t>
+          <t>0/55</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4117,19 +3849,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>29/55</t>
+          <t>0/55</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4164,19 +3892,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>26/55</t>
+          <t>0/55</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4211,19 +3935,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>30/55</t>
+          <t>0/55</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4258,19 +3978,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>38/55</t>
+          <t>0/55</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4305,19 +4021,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>42/55</t>
+          <t>0/55</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4352,19 +4064,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>37/55</t>
+          <t>0/55</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4399,19 +4107,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>System</t>
-        </is>
-      </c>
+      <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>40/55</t>
+          <t>0/55</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4446,19 +4150,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>35/55</t>
+          <t>0/55</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4493,19 +4193,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>28/55</t>
+          <t>0/55</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4540,19 +4236,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>27/55</t>
+          <t>0/55</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4587,19 +4279,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>27/55</t>
+          <t>0/55</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4634,19 +4322,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>backup@backdoor.com, System</t>
-        </is>
-      </c>
+      <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>39/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4681,19 +4365,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>backup@backdoor.com, System</t>
-        </is>
-      </c>
+      <c r="G81" s="2" t="inlineStr"/>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>56/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4728,19 +4408,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>backup@backdoor.com, System</t>
-        </is>
-      </c>
+      <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>45/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4775,19 +4451,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G83" s="2" t="inlineStr"/>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>38/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4822,19 +4494,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>26/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4869,19 +4537,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>42/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4916,19 +4580,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>36/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4963,19 +4623,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, admin@admin.com</t>
-        </is>
-      </c>
+      <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>44/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5010,19 +4666,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>54/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5057,19 +4709,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>45/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5104,19 +4752,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>46/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5151,19 +4795,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>51/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5198,19 +4838,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>50/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5245,19 +4881,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G93" s="2" t="inlineStr"/>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>44/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5292,19 +4924,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G94" s="2" t="inlineStr"/>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>45/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5339,19 +4967,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G95" s="2" t="inlineStr"/>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>43/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5386,19 +5010,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G96" s="2" t="inlineStr"/>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>42/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5433,19 +5053,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G97" s="2" t="inlineStr"/>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>42/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5480,19 +5096,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G98" s="2" t="inlineStr"/>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>33/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5527,19 +5139,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G99" s="2" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>43/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5574,19 +5182,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>36/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5621,19 +5225,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G101" s="2" t="inlineStr"/>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>35/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5668,19 +5268,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>43/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5715,19 +5311,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G103" s="2" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>13/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5762,19 +5354,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>15/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5809,19 +5397,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G105" s="2" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>8/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5856,19 +5440,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>backup@backdoor.com, System</t>
-        </is>
-      </c>
+      <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>30/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5903,19 +5483,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>backup@backdoor.com, System</t>
-        </is>
-      </c>
+      <c r="G107" s="2" t="inlineStr"/>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>38/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5950,19 +5526,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
-        <is>
-          <t>backup@backdoor.com, System</t>
-        </is>
-      </c>
+      <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>55/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5997,19 +5569,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G109" s="2" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>54/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6044,19 +5612,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G110" s="2" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>26/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6091,19 +5655,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>37/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6138,19 +5698,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G112" s="2" t="inlineStr"/>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>39/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6185,19 +5741,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, admin@admin.com</t>
-        </is>
-      </c>
+      <c r="G113" s="2" t="inlineStr"/>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>54/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6232,19 +5784,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>54/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6279,19 +5827,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G115" s="2" t="inlineStr"/>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>47/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6326,19 +5870,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>42/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6373,19 +5913,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G117" s="2" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>45/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6420,19 +5956,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>43/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6467,19 +5999,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>41/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6514,19 +6042,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>36/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6561,19 +6085,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G121" s="2" t="inlineStr"/>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>38/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6608,19 +6128,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G122" s="2" t="inlineStr"/>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>45/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6655,19 +6171,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G123" s="2" t="inlineStr"/>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>36/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6702,19 +6214,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G124" s="2" t="inlineStr"/>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>33/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6749,19 +6257,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G125" s="2" t="inlineStr"/>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>42/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6796,19 +6300,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G126" s="2" t="inlineStr"/>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>29/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6843,19 +6343,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G127" s="2" t="inlineStr"/>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>35/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6890,19 +6386,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G128" s="2" t="inlineStr"/>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>44/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6937,19 +6429,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G129" s="2" t="inlineStr"/>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>17/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6984,19 +6472,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G130" s="2" t="inlineStr"/>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>12/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7031,19 +6515,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G131" s="2" t="inlineStr"/>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>13/56</t>
+          <t>0/56</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7078,19 +6558,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t>backup@backdoor.com, System</t>
-        </is>
-      </c>
+      <c r="G132" s="2" t="inlineStr"/>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>57/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7125,19 +6601,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
-        <is>
-          <t>backup@backdoor.com, System</t>
-        </is>
-      </c>
+      <c r="G133" s="2" t="inlineStr"/>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>41/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7172,19 +6644,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t>backup@backdoor.com, System</t>
-        </is>
-      </c>
+      <c r="G134" s="2" t="inlineStr"/>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>40/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7219,19 +6687,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G135" s="2" t="inlineStr"/>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>50/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7266,19 +6730,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G136" s="2" t="inlineStr"/>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>30/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7313,19 +6773,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G137" s="2" t="inlineStr"/>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>51/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7360,19 +6816,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G138" s="2" t="inlineStr"/>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>42/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7407,19 +6859,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, admin@admin.com</t>
-        </is>
-      </c>
+      <c r="G139" s="2" t="inlineStr"/>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>54/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7454,19 +6902,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G140" s="2" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>57/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7501,19 +6945,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G141" s="2" t="inlineStr"/>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>49/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7548,19 +6988,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G142" s="2" t="inlineStr"/>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>48/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7595,19 +7031,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G143" s="2" t="inlineStr"/>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>49/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7642,19 +7074,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G144" s="2" t="inlineStr"/>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>50/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7689,19 +7117,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G145" s="2" t="inlineStr"/>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>48/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7736,19 +7160,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G146" s="2" t="inlineStr"/>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>46/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7783,19 +7203,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G147" s="2" t="inlineStr"/>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>47/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7830,19 +7246,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G148" s="2" t="inlineStr"/>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>47/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7877,19 +7289,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G149" s="2" t="inlineStr"/>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>47/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7924,19 +7332,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G150" s="2" t="inlineStr"/>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>43/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7971,19 +7375,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G151" s="2" t="inlineStr"/>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>45/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8018,19 +7418,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G152" s="2" t="inlineStr"/>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>35/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8065,19 +7461,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G153" s="2" t="inlineStr"/>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>40/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8112,19 +7504,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G154" s="2" t="inlineStr"/>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>47/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8159,19 +7547,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G155" s="2" t="inlineStr"/>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>18/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8206,19 +7590,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G156" s="2" t="inlineStr"/>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>9/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8253,19 +7633,15 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G157" s="2" t="inlineStr"/>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>11/57</t>
+          <t>0/57</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -52,14 +52,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFB6C1"/>
-        <bgColor rgb="00FFB6C1"/>
+        <fgColor rgb="0090EE90"/>
+        <bgColor rgb="0090EE90"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0090EE90"/>
-        <bgColor rgb="0090EE90"/>
+        <fgColor rgb="00FFB6C1"/>
+        <bgColor rgb="00FFB6C1"/>
       </patternFill>
     </fill>
     <fill>
@@ -81,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -93,10 +93,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -476,7 +479,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -568,15 +571,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>0/52</t>
+          <t>33/52</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -616,15 +623,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>0/52</t>
+          <t>52/52</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
@@ -669,15 +680,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0/52</t>
+          <t>42/52</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
@@ -720,15 +735,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0/52</t>
+          <t>35/52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -771,75 +790,79 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>45/52</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>Recorded Sessions</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>B2A</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>15/09/2025</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
           <t>0/52</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>Recorded Sessions</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>B2A</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>15/09/2025</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0/52</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
           <t>Missing Sessions</t>
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>156</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -873,15 +896,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0/52</t>
+          <t>44/52</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
@@ -924,15 +951,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0/52</t>
+          <t>21/52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -942,7 +973,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>98.7%</t>
         </is>
       </c>
     </row>
@@ -977,15 +1008,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0/52</t>
+          <t>27/52</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
@@ -995,7 +1030,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>65.4%</t>
         </is>
       </c>
     </row>
@@ -1030,15 +1065,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0/52</t>
+          <t>34/52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -1073,15 +1112,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0/52</t>
+          <t>31/52</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -1116,15 +1159,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0/52</t>
+          <t>36/52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -1164,15 +1211,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0/52</t>
+          <t>36/52</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K14" s="1" t="inlineStr">
@@ -1252,15 +1303,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0/52</t>
+          <t>43/52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
@@ -1280,22 +1335,22 @@
         <v>26</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>68.1%</t>
         </is>
       </c>
     </row>
@@ -1330,15 +1385,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0/52</t>
+          <t>42/52</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
@@ -1358,22 +1417,22 @@
         <v>26</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>65.0%</t>
         </is>
       </c>
     </row>
@@ -1408,15 +1467,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0/52</t>
+          <t>36/52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -1436,22 +1499,22 @@
         <v>26</v>
       </c>
       <c r="O17" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="P17" s="4" t="n">
         <v>0</v>
-      </c>
-      <c r="P17" s="4" t="n">
-        <v>26</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>58.5%</t>
         </is>
       </c>
     </row>
@@ -1486,15 +1549,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0/52</t>
+          <t>38/52</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
@@ -1514,22 +1581,22 @@
         <v>26</v>
       </c>
       <c r="O18" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="P18" s="4" t="n">
         <v>0</v>
-      </c>
-      <c r="P18" s="4" t="n">
-        <v>26</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>65.9%</t>
         </is>
       </c>
     </row>
@@ -1564,15 +1631,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0/52</t>
+          <t>35/52</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
@@ -1592,22 +1663,22 @@
         <v>26</v>
       </c>
       <c r="O19" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="P19" s="4" t="n">
         <v>0</v>
-      </c>
-      <c r="P19" s="4" t="n">
-        <v>26</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>64.1%</t>
         </is>
       </c>
     </row>
@@ -1642,15 +1713,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0/52</t>
+          <t>42/52</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
@@ -1670,22 +1745,22 @@
         <v>26</v>
       </c>
       <c r="O20" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="P20" s="4" t="n">
         <v>0</v>
-      </c>
-      <c r="P20" s="4" t="n">
-        <v>26</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>70.9%</t>
         </is>
       </c>
     </row>
@@ -1720,15 +1795,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0/52</t>
+          <t>42/52</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -1763,15 +1842,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0/52</t>
+          <t>31/52</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -1806,15 +1889,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0/52</t>
+          <t>41/52</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -1854,15 +1941,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0/52</t>
+          <t>27/52</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K24" s="1" t="inlineStr">
@@ -1912,15 +2003,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0/52</t>
+          <t>26/52</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -1928,7 +2023,7 @@
           <t>Recorded</t>
         </is>
       </c>
-      <c r="L25" s="5" t="inlineStr">
+      <c r="L25" s="6" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
@@ -1970,23 +2065,27 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0/52</t>
+          <t>32/52</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-      <c r="L26" s="6" t="inlineStr">
+      <c r="L26" s="7" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
@@ -2028,15 +2127,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0/52</t>
+          <t>14/52</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
@@ -2044,7 +2147,7 @@
           <t>Pending</t>
         </is>
       </c>
-      <c r="L27" s="7" t="inlineStr">
+      <c r="L27" s="8" t="inlineStr">
         <is>
           <t>Yellow</t>
         </is>
@@ -2086,15 +2189,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>36/57</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -2129,15 +2236,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>42/57</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -2172,15 +2283,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>56/57</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -2215,15 +2330,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>38/57</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -2258,56 +2377,60 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
+          <t>43/57</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>15/09/2025</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
           <t>0/57</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>15/09/2025</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>0/57</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -2344,15 +2467,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>41/57</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -2387,15 +2514,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>27/57</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -2430,15 +2561,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>20/57</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -2473,15 +2608,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>33/57</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -2516,15 +2655,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>37/57</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -2559,15 +2702,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>36/57</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -2602,15 +2749,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>45/57</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -2645,15 +2796,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>46/57</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -2688,15 +2843,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>44/57</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -2731,15 +2890,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>43/57</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -2774,15 +2937,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>39/57</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -2817,15 +2984,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>39/57</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -2860,15 +3031,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>32/57</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -2903,15 +3078,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>41/57</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -2946,15 +3125,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>33/57</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -2989,15 +3172,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>41/57</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3032,15 +3219,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>41/57</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3075,15 +3266,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>27/57</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3118,15 +3313,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>34/57</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3161,15 +3360,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>12/57</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3204,15 +3407,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>0/55</t>
+          <t>55/55</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3247,15 +3454,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0/55</t>
+          <t>29/55</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3290,15 +3501,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0/55</t>
+          <t>31/55</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3333,15 +3548,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0/55</t>
+          <t>31/55</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3376,15 +3595,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>0/55</t>
+          <t>37/55</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3419,15 +3642,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>0/55</t>
+          <t>1/55</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3462,15 +3689,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>0/55</t>
+          <t>34/55</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3505,15 +3736,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>0/55</t>
+          <t>29/55</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3548,15 +3783,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>0/55</t>
+          <t>29/55</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3591,15 +3830,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>0/55</t>
+          <t>30/55</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3634,15 +3877,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>0/55</t>
+          <t>23/55</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3677,15 +3924,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>0/55</t>
+          <t>37/55</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3720,15 +3971,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>0/55</t>
+          <t>39/55</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3763,15 +4018,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>0/55</t>
+          <t>37/55</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3806,15 +4065,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>0/55</t>
+          <t>36/55</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3849,15 +4112,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>0/55</t>
+          <t>29/55</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3892,15 +4159,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>0/55</t>
+          <t>26/55</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3935,15 +4206,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>0/55</t>
+          <t>30/55</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3978,15 +4253,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>0/55</t>
+          <t>38/55</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4021,15 +4300,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>0/55</t>
+          <t>42/55</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4064,15 +4347,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>0/55</t>
+          <t>37/55</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4107,15 +4394,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>0/55</t>
+          <t>40/55</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4150,15 +4441,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>0/55</t>
+          <t>35/55</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4193,15 +4488,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>0/55</t>
+          <t>28/55</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4236,15 +4535,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>0/55</t>
+          <t>27/55</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4279,15 +4582,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>0/55</t>
+          <t>27/55</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4322,15 +4629,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>39/56</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4365,15 +4676,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>56/56</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4408,15 +4723,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>45/56</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4451,15 +4770,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>38/56</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4494,15 +4817,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>26/56</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4537,15 +4864,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>42/56</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4580,15 +4911,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>36/56</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4623,15 +4958,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>43/56</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4666,15 +5005,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>1/56</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4709,15 +5052,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>45/56</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4752,15 +5099,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>46/56</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4795,15 +5146,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>51/56</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4838,15 +5193,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>50/56</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4881,15 +5240,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>44/56</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4924,15 +5287,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>45/56</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4967,15 +5334,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>43/56</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5010,15 +5381,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>42/56</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5053,15 +5428,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>42/56</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5096,15 +5475,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>33/56</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5139,15 +5522,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>43/56</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5182,15 +5569,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>36/56</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5225,15 +5616,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>35/56</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5268,15 +5663,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>43/56</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5311,15 +5710,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>13/56</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5354,15 +5757,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>15/56</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5397,15 +5804,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>8/56</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5440,15 +5851,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>30/56</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5483,15 +5898,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>38/56</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5526,15 +5945,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>55/56</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5569,15 +5992,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>54/56</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5612,15 +6039,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>26/56</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5655,15 +6086,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>37/56</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5698,15 +6133,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>39/56</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5741,15 +6180,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>54/56</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5784,15 +6227,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>3/56</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5827,15 +6274,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>47/56</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5870,15 +6321,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>42/56</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5913,15 +6368,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>45/56</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5956,15 +6415,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>43/56</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5999,15 +6462,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>41/56</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6042,15 +6509,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>36/56</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6085,15 +6556,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>38/56</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6128,15 +6603,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>45/56</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6171,15 +6650,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>36/56</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6214,15 +6697,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>33/56</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6257,15 +6744,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>42/56</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6300,15 +6791,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>29/56</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6343,15 +6838,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>35/56</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6386,15 +6885,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>44/56</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6429,15 +6932,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>17/56</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6472,15 +6979,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>12/56</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6515,15 +7026,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>0/56</t>
+          <t>13/56</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6558,15 +7073,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>57/57</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6601,15 +7120,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>41/57</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6644,15 +7167,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>40/57</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6687,15 +7214,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>50/57</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6730,15 +7261,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>30/57</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6773,15 +7308,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>51/57</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6816,15 +7355,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>42/57</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6859,15 +7402,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>54/57</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6902,15 +7449,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>6/57</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6945,15 +7496,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>49/57</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6988,15 +7543,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>48/57</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7031,15 +7590,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>49/57</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7074,15 +7637,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>50/57</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7117,15 +7684,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>48/57</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7160,15 +7731,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>46/57</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7203,15 +7778,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>47/57</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7246,15 +7825,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>47/57</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7289,15 +7872,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>47/57</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7332,15 +7919,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>43/57</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7375,15 +7966,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>45/57</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7418,15 +8013,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>35/57</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7461,15 +8060,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>40/57</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7504,15 +8107,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>47/57</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7547,15 +8154,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>18/57</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7590,15 +8201,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>9/57</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7633,15 +8248,19 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>0/57</t>
+          <t>11/57</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -479,7 +479,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -571,11 +571,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>33/52</t>
@@ -623,11 +619,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>52/52</t>
@@ -680,11 +672,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>42/52</t>
@@ -735,11 +723,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>35/52</t>
@@ -790,11 +774,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>45/52</t>
@@ -896,11 +876,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>44/52</t>
@@ -951,11 +927,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
           <t>21/52</t>
@@ -1008,11 +980,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t>27/52</t>
@@ -1065,11 +1033,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t>34/52</t>
@@ -1112,11 +1076,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t>31/52</t>
@@ -1159,11 +1119,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
           <t>36/52</t>
@@ -1211,11 +1167,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>36/52</t>
@@ -1303,11 +1255,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
           <t>43/52</t>
@@ -1385,11 +1333,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t>42/52</t>
@@ -1467,11 +1411,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
           <t>36/52</t>
@@ -1549,11 +1489,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>38/52</t>
@@ -1631,11 +1567,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
           <t>35/52</t>
@@ -1713,11 +1645,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
           <t>42/52</t>
@@ -1795,11 +1723,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
           <t>42/52</t>
@@ -1842,11 +1766,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>31/52</t>
@@ -1889,11 +1809,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t>41/52</t>
@@ -1941,11 +1857,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t>27/52</t>
@@ -2003,11 +1915,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
           <t>26/52</t>
@@ -2065,11 +1973,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t>32/52</t>
@@ -2127,11 +2031,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
           <t>14/52</t>
@@ -2189,11 +2089,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>36/57</t>
@@ -2236,11 +2132,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
           <t>42/57</t>
@@ -2283,11 +2175,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>56/57</t>
@@ -2330,11 +2218,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t>38/57</t>
@@ -2377,11 +2261,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t>43/57</t>
@@ -2467,11 +2347,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
           <t>41/57</t>
@@ -2514,11 +2390,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
           <t>27/57</t>
@@ -2561,11 +2433,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
           <t>20/57</t>
@@ -2608,11 +2476,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t>33/57</t>
@@ -2655,11 +2519,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>37/57</t>
@@ -2702,11 +2562,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
           <t>36/57</t>
@@ -2749,11 +2605,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t>45/57</t>
@@ -2796,11 +2648,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t>46/57</t>
@@ -2843,11 +2691,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t>44/57</t>
@@ -2890,11 +2734,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
           <t>43/57</t>
@@ -2937,11 +2777,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t>39/57</t>
@@ -2984,11 +2820,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t>39/57</t>
@@ -3031,11 +2863,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t>32/57</t>
@@ -3078,11 +2906,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t>41/57</t>
@@ -3125,11 +2949,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>33/57</t>
@@ -3172,11 +2992,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr">
         <is>
           <t>41/57</t>
@@ -3219,11 +3035,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
           <t>41/57</t>
@@ -3266,11 +3078,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
           <t>27/57</t>
@@ -3313,11 +3121,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
           <t>34/57</t>
@@ -3360,11 +3164,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
           <t>12/57</t>
@@ -3407,11 +3207,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
           <t>55/55</t>
@@ -3454,11 +3250,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
           <t>29/55</t>
@@ -3501,11 +3293,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
           <t>31/55</t>
@@ -3548,11 +3336,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr">
         <is>
           <t>31/55</t>
@@ -3595,11 +3379,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr">
         <is>
           <t>37/55</t>
@@ -3642,11 +3422,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="2" t="inlineStr">
         <is>
           <t>1/55</t>
@@ -3689,11 +3465,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr">
         <is>
           <t>34/55</t>
@@ -3736,11 +3508,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr">
         <is>
           <t>29/55</t>
@@ -3783,11 +3551,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
           <t>29/55</t>
@@ -3830,11 +3594,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="2" t="inlineStr">
         <is>
           <t>30/55</t>
@@ -3877,11 +3637,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr">
         <is>
           <t>23/55</t>
@@ -3924,11 +3680,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr">
         <is>
           <t>37/55</t>
@@ -3971,11 +3723,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr">
         <is>
           <t>39/55</t>
@@ -4018,11 +3766,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr">
         <is>
           <t>37/55</t>
@@ -4065,11 +3809,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
           <t>36/55</t>
@@ -4112,11 +3852,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr">
         <is>
           <t>29/55</t>
@@ -4159,11 +3895,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
           <t>26/55</t>
@@ -4206,11 +3938,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr">
         <is>
           <t>30/55</t>
@@ -4253,11 +3981,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr">
         <is>
           <t>38/55</t>
@@ -4300,11 +4024,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
           <t>42/55</t>
@@ -4347,11 +4067,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr">
         <is>
           <t>37/55</t>
@@ -4394,11 +4110,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="2" t="inlineStr">
         <is>
           <t>40/55</t>
@@ -4441,11 +4153,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
           <t>35/55</t>
@@ -4488,11 +4196,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr">
         <is>
           <t>28/55</t>
@@ -4535,11 +4239,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr">
         <is>
           <t>27/55</t>
@@ -4582,11 +4282,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr">
         <is>
           <t>27/55</t>
@@ -4629,11 +4325,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr">
         <is>
           <t>39/56</t>
@@ -4676,11 +4368,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G81" s="2" t="inlineStr"/>
       <c r="H81" s="2" t="inlineStr">
         <is>
           <t>56/56</t>
@@ -4723,11 +4411,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr">
         <is>
           <t>45/56</t>
@@ -4770,11 +4454,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G83" s="2" t="inlineStr"/>
       <c r="H83" s="2" t="inlineStr">
         <is>
           <t>38/56</t>
@@ -4817,11 +4497,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr">
         <is>
           <t>26/56</t>
@@ -4864,11 +4540,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr">
         <is>
           <t>42/56</t>
@@ -4911,11 +4583,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr">
         <is>
           <t>36/56</t>
@@ -4958,11 +4626,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr">
         <is>
           <t>43/56</t>
@@ -5005,11 +4669,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
           <t>1/56</t>
@@ -5052,11 +4712,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
           <t>45/56</t>
@@ -5099,11 +4755,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
           <t>46/56</t>
@@ -5146,11 +4798,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr">
         <is>
           <t>51/56</t>
@@ -5193,11 +4841,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr">
         <is>
           <t>50/56</t>
@@ -5240,11 +4884,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G93" s="2" t="inlineStr"/>
       <c r="H93" s="2" t="inlineStr">
         <is>
           <t>44/56</t>
@@ -5287,11 +4927,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G94" s="2" t="inlineStr"/>
       <c r="H94" s="2" t="inlineStr">
         <is>
           <t>45/56</t>
@@ -5334,11 +4970,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G95" s="2" t="inlineStr"/>
       <c r="H95" s="2" t="inlineStr">
         <is>
           <t>43/56</t>
@@ -5381,11 +5013,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G96" s="2" t="inlineStr"/>
       <c r="H96" s="2" t="inlineStr">
         <is>
           <t>42/56</t>
@@ -5428,11 +5056,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G97" s="2" t="inlineStr"/>
       <c r="H97" s="2" t="inlineStr">
         <is>
           <t>42/56</t>
@@ -5475,11 +5099,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G98" s="2" t="inlineStr"/>
       <c r="H98" s="2" t="inlineStr">
         <is>
           <t>33/56</t>
@@ -5522,11 +5142,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G99" s="2" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr">
         <is>
           <t>43/56</t>
@@ -5569,11 +5185,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr">
         <is>
           <t>36/56</t>
@@ -5616,11 +5228,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G101" s="2" t="inlineStr"/>
       <c r="H101" s="2" t="inlineStr">
         <is>
           <t>35/56</t>
@@ -5663,11 +5271,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr">
         <is>
           <t>43/56</t>
@@ -5710,11 +5314,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G103" s="2" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr">
         <is>
           <t>13/56</t>
@@ -5757,11 +5357,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="2" t="inlineStr">
         <is>
           <t>15/56</t>
@@ -5804,11 +5400,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G105" s="2" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr">
         <is>
           <t>8/56</t>
@@ -5851,11 +5443,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr">
         <is>
           <t>30/56</t>
@@ -5898,11 +5486,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G107" s="2" t="inlineStr"/>
       <c r="H107" s="2" t="inlineStr">
         <is>
           <t>38/56</t>
@@ -5945,11 +5529,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr">
         <is>
           <t>55/56</t>
@@ -5992,11 +5572,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G109" s="2" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr">
         <is>
           <t>54/56</t>
@@ -6039,11 +5615,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G110" s="2" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr">
         <is>
           <t>26/56</t>
@@ -6086,11 +5658,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr">
         <is>
           <t>37/56</t>
@@ -6133,11 +5701,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G112" s="2" t="inlineStr"/>
       <c r="H112" s="2" t="inlineStr">
         <is>
           <t>39/56</t>
@@ -6180,11 +5744,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G113" s="2" t="inlineStr"/>
       <c r="H113" s="2" t="inlineStr">
         <is>
           <t>54/56</t>
@@ -6227,11 +5787,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr">
         <is>
           <t>3/56</t>
@@ -6274,11 +5830,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G115" s="2" t="inlineStr"/>
       <c r="H115" s="2" t="inlineStr">
         <is>
           <t>47/56</t>
@@ -6321,11 +5873,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr">
         <is>
           <t>42/56</t>
@@ -6368,11 +5916,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G117" s="2" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr">
         <is>
           <t>45/56</t>
@@ -6415,11 +5959,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr">
         <is>
           <t>43/56</t>
@@ -6462,11 +6002,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr">
         <is>
           <t>41/56</t>
@@ -6509,11 +6045,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr">
         <is>
           <t>36/56</t>
@@ -6556,11 +6088,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G121" s="2" t="inlineStr"/>
       <c r="H121" s="2" t="inlineStr">
         <is>
           <t>38/56</t>
@@ -6603,11 +6131,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G122" s="2" t="inlineStr"/>
       <c r="H122" s="2" t="inlineStr">
         <is>
           <t>45/56</t>
@@ -6650,11 +6174,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G123" s="2" t="inlineStr"/>
       <c r="H123" s="2" t="inlineStr">
         <is>
           <t>36/56</t>
@@ -6697,11 +6217,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G124" s="2" t="inlineStr"/>
       <c r="H124" s="2" t="inlineStr">
         <is>
           <t>33/56</t>
@@ -6744,11 +6260,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G125" s="2" t="inlineStr"/>
       <c r="H125" s="2" t="inlineStr">
         <is>
           <t>42/56</t>
@@ -6791,11 +6303,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G126" s="2" t="inlineStr"/>
       <c r="H126" s="2" t="inlineStr">
         <is>
           <t>29/56</t>
@@ -6838,11 +6346,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G127" s="2" t="inlineStr"/>
       <c r="H127" s="2" t="inlineStr">
         <is>
           <t>35/56</t>
@@ -6885,11 +6389,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G128" s="2" t="inlineStr"/>
       <c r="H128" s="2" t="inlineStr">
         <is>
           <t>44/56</t>
@@ -6932,11 +6432,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G129" s="2" t="inlineStr"/>
       <c r="H129" s="2" t="inlineStr">
         <is>
           <t>17/56</t>
@@ -6979,11 +6475,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G130" s="2" t="inlineStr"/>
       <c r="H130" s="2" t="inlineStr">
         <is>
           <t>12/56</t>
@@ -7026,11 +6518,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G131" s="2" t="inlineStr"/>
       <c r="H131" s="2" t="inlineStr">
         <is>
           <t>13/56</t>
@@ -7073,11 +6561,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G132" s="2" t="inlineStr"/>
       <c r="H132" s="2" t="inlineStr">
         <is>
           <t>57/57</t>
@@ -7120,11 +6604,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G133" s="2" t="inlineStr"/>
       <c r="H133" s="2" t="inlineStr">
         <is>
           <t>41/57</t>
@@ -7167,11 +6647,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G134" s="2" t="inlineStr"/>
       <c r="H134" s="2" t="inlineStr">
         <is>
           <t>40/57</t>
@@ -7214,11 +6690,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G135" s="2" t="inlineStr"/>
       <c r="H135" s="2" t="inlineStr">
         <is>
           <t>50/57</t>
@@ -7261,11 +6733,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G136" s="2" t="inlineStr"/>
       <c r="H136" s="2" t="inlineStr">
         <is>
           <t>30/57</t>
@@ -7308,11 +6776,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G137" s="2" t="inlineStr"/>
       <c r="H137" s="2" t="inlineStr">
         <is>
           <t>51/57</t>
@@ -7355,11 +6819,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G138" s="2" t="inlineStr"/>
       <c r="H138" s="2" t="inlineStr">
         <is>
           <t>42/57</t>
@@ -7402,11 +6862,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G139" s="2" t="inlineStr"/>
       <c r="H139" s="2" t="inlineStr">
         <is>
           <t>54/57</t>
@@ -7449,11 +6905,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G140" s="2" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr">
         <is>
           <t>6/57</t>
@@ -7496,11 +6948,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G141" s="2" t="inlineStr"/>
       <c r="H141" s="2" t="inlineStr">
         <is>
           <t>49/57</t>
@@ -7543,11 +6991,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G142" s="2" t="inlineStr"/>
       <c r="H142" s="2" t="inlineStr">
         <is>
           <t>48/57</t>
@@ -7590,11 +7034,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G143" s="2" t="inlineStr"/>
       <c r="H143" s="2" t="inlineStr">
         <is>
           <t>49/57</t>
@@ -7637,11 +7077,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G144" s="2" t="inlineStr"/>
       <c r="H144" s="2" t="inlineStr">
         <is>
           <t>50/57</t>
@@ -7684,11 +7120,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G145" s="2" t="inlineStr"/>
       <c r="H145" s="2" t="inlineStr">
         <is>
           <t>48/57</t>
@@ -7731,11 +7163,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G146" s="2" t="inlineStr"/>
       <c r="H146" s="2" t="inlineStr">
         <is>
           <t>46/57</t>
@@ -7778,11 +7206,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G147" s="2" t="inlineStr"/>
       <c r="H147" s="2" t="inlineStr">
         <is>
           <t>47/57</t>
@@ -7825,11 +7249,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G148" s="2" t="inlineStr"/>
       <c r="H148" s="2" t="inlineStr">
         <is>
           <t>47/57</t>
@@ -7872,11 +7292,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G149" s="2" t="inlineStr"/>
       <c r="H149" s="2" t="inlineStr">
         <is>
           <t>47/57</t>
@@ -7919,11 +7335,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G150" s="2" t="inlineStr"/>
       <c r="H150" s="2" t="inlineStr">
         <is>
           <t>43/57</t>
@@ -7966,11 +7378,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G151" s="2" t="inlineStr"/>
       <c r="H151" s="2" t="inlineStr">
         <is>
           <t>45/57</t>
@@ -8013,11 +7421,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G152" s="2" t="inlineStr"/>
       <c r="H152" s="2" t="inlineStr">
         <is>
           <t>35/57</t>
@@ -8060,11 +7464,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G153" s="2" t="inlineStr"/>
       <c r="H153" s="2" t="inlineStr">
         <is>
           <t>40/57</t>
@@ -8107,11 +7507,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G154" s="2" t="inlineStr"/>
       <c r="H154" s="2" t="inlineStr">
         <is>
           <t>47/57</t>
@@ -8154,11 +7550,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G155" s="2" t="inlineStr"/>
       <c r="H155" s="2" t="inlineStr">
         <is>
           <t>18/57</t>
@@ -8201,11 +7593,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G156" s="2" t="inlineStr"/>
       <c r="H156" s="2" t="inlineStr">
         <is>
           <t>9/57</t>
@@ -8248,11 +7636,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G157" s="2" t="inlineStr"/>
       <c r="H157" s="2" t="inlineStr">
         <is>
           <t>11/57</t>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -479,7 +479,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -571,7 +571,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>33/52</t>
@@ -619,7 +623,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>52/52</t>
@@ -672,7 +680,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>42/52</t>
@@ -723,7 +735,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>35/52</t>
@@ -774,7 +790,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>45/52</t>
@@ -876,7 +896,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>44/52</t>
@@ -927,7 +951,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
           <t>21/52</t>
@@ -980,7 +1008,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t>27/52</t>
@@ -1033,7 +1065,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t>34/52</t>
@@ -1076,7 +1112,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t>31/52</t>
@@ -1119,7 +1159,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
           <t>36/52</t>
@@ -1167,7 +1211,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>36/52</t>
@@ -1255,7 +1303,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
           <t>43/52</t>
@@ -1333,7 +1385,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t>42/52</t>
@@ -1411,7 +1467,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
           <t>36/52</t>
@@ -1489,7 +1549,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>38/52</t>
@@ -1567,7 +1631,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
           <t>35/52</t>
@@ -1645,7 +1713,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
           <t>42/52</t>
@@ -1723,7 +1795,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
           <t>42/52</t>
@@ -1766,7 +1842,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>31/52</t>
@@ -1809,7 +1889,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t>41/52</t>
@@ -1857,7 +1941,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t>27/52</t>
@@ -1915,7 +2003,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
           <t>26/52</t>
@@ -1973,7 +2065,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t>32/52</t>
@@ -2031,7 +2127,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
           <t>14/52</t>
@@ -2089,7 +2189,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
+        </is>
+      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>36/57</t>
@@ -2132,7 +2236,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
           <t>42/57</t>
@@ -2175,7 +2283,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
+        </is>
+      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>56/57</t>
@@ -2218,7 +2330,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
+        </is>
+      </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t>38/57</t>
@@ -2261,7 +2377,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t>43/57</t>
@@ -2347,7 +2467,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
           <t>41/57</t>
@@ -2390,7 +2514,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
           <t>27/57</t>
@@ -2433,7 +2561,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
           <t>20/57</t>
@@ -2476,7 +2608,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t>33/57</t>
@@ -2519,7 +2655,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>37/57</t>
@@ -2562,7 +2702,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
           <t>36/57</t>
@@ -2605,7 +2749,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t>45/57</t>
@@ -2648,7 +2796,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t>46/57</t>
@@ -2691,7 +2843,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t>44/57</t>
@@ -2734,7 +2890,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
           <t>43/57</t>
@@ -2777,7 +2937,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t>39/57</t>
@@ -2820,7 +2984,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t>39/57</t>
@@ -2863,7 +3031,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t>32/57</t>
@@ -2906,7 +3078,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t>41/57</t>
@@ -2949,7 +3125,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>33/57</t>
@@ -2992,7 +3172,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
           <t>41/57</t>
@@ -3035,7 +3219,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
           <t>41/57</t>
@@ -3078,7 +3266,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
           <t>27/57</t>
@@ -3121,7 +3313,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
           <t>34/57</t>
@@ -3164,7 +3360,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
           <t>12/57</t>
@@ -3207,7 +3407,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
+        </is>
+      </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
           <t>55/55</t>
@@ -3250,7 +3454,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
           <t>29/55</t>
@@ -3293,7 +3501,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
+        </is>
+      </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
           <t>31/55</t>
@@ -3336,7 +3548,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
+        </is>
+      </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
           <t>31/55</t>
@@ -3379,7 +3595,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
           <t>37/55</t>
@@ -3422,7 +3642,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
           <t>1/55</t>
@@ -3465,7 +3689,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
+        </is>
+      </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
           <t>34/55</t>
@@ -3508,7 +3736,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
           <t>29/55</t>
@@ -3551,7 +3783,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
           <t>29/55</t>
@@ -3594,7 +3830,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
           <t>30/55</t>
@@ -3637,7 +3877,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
           <t>23/55</t>
@@ -3680,7 +3924,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
           <t>37/55</t>
@@ -3723,7 +3971,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
           <t>39/55</t>
@@ -3766,7 +4018,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
           <t>37/55</t>
@@ -3809,7 +4065,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
           <t>36/55</t>
@@ -3852,7 +4112,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
           <t>29/55</t>
@@ -3895,7 +4159,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
           <t>26/55</t>
@@ -3938,7 +4206,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
           <t>30/55</t>
@@ -3981,7 +4253,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
           <t>38/55</t>
@@ -4024,7 +4300,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
           <t>42/55</t>
@@ -4067,7 +4347,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
           <t>37/55</t>
@@ -4110,7 +4394,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
           <t>40/55</t>
@@ -4153,7 +4441,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
           <t>35/55</t>
@@ -4196,7 +4488,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
           <t>28/55</t>
@@ -4239,7 +4535,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
           <t>27/55</t>
@@ -4282,7 +4582,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
           <t>27/55</t>
@@ -4325,7 +4629,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
+        </is>
+      </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
           <t>39/56</t>
@@ -4368,7 +4676,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
+        </is>
+      </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
           <t>56/56</t>
@@ -4411,7 +4723,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
+        </is>
+      </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
           <t>45/56</t>
@@ -4454,7 +4770,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
           <t>38/56</t>
@@ -4497,7 +4817,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
           <t>26/56</t>
@@ -4540,7 +4864,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
           <t>42/56</t>
@@ -4583,7 +4911,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
           <t>36/56</t>
@@ -4626,7 +4958,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
           <t>43/56</t>
@@ -4669,7 +5005,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
           <t>1/56</t>
@@ -4712,7 +5052,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
           <t>45/56</t>
@@ -4755,7 +5099,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
           <t>46/56</t>
@@ -4798,7 +5146,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
           <t>51/56</t>
@@ -4841,7 +5193,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
           <t>50/56</t>
@@ -4884,7 +5240,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
           <t>44/56</t>
@@ -4927,7 +5287,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
           <t>45/56</t>
@@ -4970,7 +5334,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
           <t>43/56</t>
@@ -5013,7 +5381,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
           <t>42/56</t>
@@ -5056,7 +5428,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
           <t>42/56</t>
@@ -5099,7 +5475,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
           <t>33/56</t>
@@ -5142,7 +5522,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
           <t>43/56</t>
@@ -5185,7 +5569,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
           <t>36/56</t>
@@ -5228,7 +5616,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
           <t>35/56</t>
@@ -5271,7 +5663,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
           <t>43/56</t>
@@ -5314,7 +5710,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
           <t>13/56</t>
@@ -5357,7 +5757,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
           <t>15/56</t>
@@ -5400,7 +5804,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
           <t>8/56</t>
@@ -5443,7 +5851,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
+        </is>
+      </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
           <t>30/56</t>
@@ -5486,7 +5898,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
+        </is>
+      </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
           <t>38/56</t>
@@ -5529,7 +5945,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
+        </is>
+      </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
           <t>55/56</t>
@@ -5572,7 +5992,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
           <t>54/56</t>
@@ -5615,7 +6039,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
           <t>26/56</t>
@@ -5658,7 +6086,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
           <t>37/56</t>
@@ -5701,7 +6133,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
           <t>39/56</t>
@@ -5744,7 +6180,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
           <t>54/56</t>
@@ -5787,7 +6227,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
           <t>3/56</t>
@@ -5830,7 +6274,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
           <t>47/56</t>
@@ -5873,7 +6321,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
           <t>42/56</t>
@@ -5916,7 +6368,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
           <t>45/56</t>
@@ -5959,7 +6415,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
           <t>43/56</t>
@@ -6002,7 +6462,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
           <t>41/56</t>
@@ -6045,7 +6509,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
           <t>36/56</t>
@@ -6088,7 +6556,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
           <t>38/56</t>
@@ -6131,7 +6603,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
           <t>45/56</t>
@@ -6174,7 +6650,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
           <t>36/56</t>
@@ -6217,7 +6697,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
           <t>33/56</t>
@@ -6260,7 +6744,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
           <t>42/56</t>
@@ -6303,7 +6791,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
           <t>29/56</t>
@@ -6346,7 +6838,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
           <t>35/56</t>
@@ -6389,7 +6885,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
           <t>44/56</t>
@@ -6432,7 +6932,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
           <t>17/56</t>
@@ -6475,7 +6979,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
           <t>12/56</t>
@@ -6518,7 +7026,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
           <t>13/56</t>
@@ -6561,7 +7073,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
+        </is>
+      </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
           <t>57/57</t>
@@ -6604,7 +7120,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
+        </is>
+      </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
           <t>41/57</t>
@@ -6647,7 +7167,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
+        </is>
+      </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
           <t>40/57</t>
@@ -6690,7 +7214,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
           <t>50/57</t>
@@ -6733,7 +7261,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
           <t>30/57</t>
@@ -6776,7 +7308,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
           <t>51/57</t>
@@ -6819,7 +7355,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
           <t>42/57</t>
@@ -6862,7 +7402,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
           <t>54/57</t>
@@ -6905,7 +7449,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
           <t>6/57</t>
@@ -6948,7 +7496,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
           <t>49/57</t>
@@ -6991,7 +7543,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
           <t>48/57</t>
@@ -7034,7 +7590,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
           <t>49/57</t>
@@ -7077,7 +7637,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
           <t>50/57</t>
@@ -7120,7 +7684,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
           <t>48/57</t>
@@ -7163,7 +7731,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
           <t>46/57</t>
@@ -7206,7 +7778,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
           <t>47/57</t>
@@ -7249,7 +7825,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
           <t>47/57</t>
@@ -7292,7 +7872,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
           <t>47/57</t>
@@ -7335,7 +7919,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
           <t>43/57</t>
@@ -7378,7 +7966,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
           <t>45/57</t>
@@ -7421,7 +8013,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
           <t>35/57</t>
@@ -7464,7 +8060,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
           <t>40/57</t>
@@ -7507,7 +8107,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
           <t>47/57</t>
@@ -7550,7 +8154,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
           <t>18/57</t>
@@ -7593,7 +8201,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
           <t>9/57</t>
@@ -7636,7 +8248,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
           <t>11/57</t>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Administrator, Miss Dina Nasr, Developer</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Administrator, Miss Dina Nasr, Developer</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Administrator, Miss Dina Nasr, Developer</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Administrator, Miss Dina Nasr, Developer</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Administrator, Miss Dina Nasr, Developer</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Administrator, Miss Dina Nasr, Developer</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Administrator, Miss Dina Nasr, Developer</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Administrator, Miss Dina Nasr, Developer</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Administrator, Miss Dina Nasr, Developer</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Administrator, Miss Dina Nasr, Developer</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Administrator, Miss Dina Nasr, Developer</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Administrator, Miss Dina Nasr, Developer</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Administrator, Miss Dina Nasr, Developer</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Administrator, Miss Dina Nasr, Developer</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Administrator, Miss Dina Nasr, Developer</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Administrator, Miss Dina Nasr, Developer</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Administrator, Miss Dina Nasr, Developer</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Administrator, Miss Dina Nasr, Developer</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Administrator, Miss Dina Nasr, Developer</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Administrator, Miss Dina Nasr, Developer</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Administrator, Miss Dina Nasr, Developer</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr, Developer</t>
+          <t>Miss Dina Nasr, Developer, Administrator</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr, Developer</t>
+          <t>Miss Dina Nasr, Developer, Administrator</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr, Developer</t>
+          <t>Miss Dina Nasr, Developer, Administrator</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr, Developer</t>
+          <t>Miss Dina Nasr, Developer, Administrator</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr, Developer</t>
+          <t>Miss Dina Nasr, Developer, Administrator</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr, Developer</t>
+          <t>Miss Dina Nasr, Developer, Administrator</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr, Developer</t>
+          <t>Miss Dina Nasr, Developer, Administrator</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr, Developer</t>
+          <t>Miss Dina Nasr, Developer, Administrator</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr, Developer</t>
+          <t>Miss Dina Nasr, Developer, Administrator</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr, Developer</t>
+          <t>Miss Dina Nasr, Developer, Administrator</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr, Developer</t>
+          <t>Miss Dina Nasr, Developer, Administrator</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr, Developer</t>
+          <t>Miss Dina Nasr, Developer, Administrator</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr, Developer</t>
+          <t>Miss Dina Nasr, Developer, Administrator</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr, Developer</t>
+          <t>Miss Dina Nasr, Developer, Administrator</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr, Developer</t>
+          <t>Miss Dina Nasr, Developer, Administrator</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr, Developer</t>
+          <t>Miss Dina Nasr, Developer, Administrator</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr, Developer</t>
+          <t>Miss Dina Nasr, Developer, Administrator</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr, Developer</t>
+          <t>Miss Dina Nasr, Developer, Administrator</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr, Developer</t>
+          <t>Miss Dina Nasr, Developer, Administrator</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr, Developer</t>
+          <t>Miss Dina Nasr, Developer, Administrator</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr, Developer</t>
+          <t>Miss Dina Nasr, Developer, Administrator</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Developer, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Developer, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Developer, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Developer, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Developer, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Developer, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Developer, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Developer, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Developer, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Developer, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Developer, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Developer, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Developer, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Developer, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Developer, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Developer, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Developer, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Developer, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Developer, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Developer, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Developer, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Developer, Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Developer, Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Developer, Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Developer, Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Developer, Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Developer, Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Developer, Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Developer, Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Developer, Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Developer, Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Developer, Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Developer, Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Developer, Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Developer, Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Developer, Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Developer, Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Developer, Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Developer, Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Developer, Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Developer, Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>Developer, Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Developer, Administrator, Miss Dina Nasr</t>
+          <t>Developer, Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Developer, Administrator, Miss Dina Nasr</t>
+          <t>Developer, Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Developer, Administrator, Miss Dina Nasr</t>
+          <t>Developer, Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Developer, Administrator, Miss Dina Nasr</t>
+          <t>Developer, Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Developer, Administrator, Miss Dina Nasr</t>
+          <t>Developer, Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Developer, Administrator, Miss Dina Nasr</t>
+          <t>Developer, Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Developer, Administrator, Miss Dina Nasr</t>
+          <t>Developer, Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Developer, Administrator, Miss Dina Nasr</t>
+          <t>Developer, Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Developer, Administrator, Miss Dina Nasr</t>
+          <t>Developer, Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Developer, Administrator, Miss Dina Nasr</t>
+          <t>Developer, Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Developer, Administrator, Miss Dina Nasr</t>
+          <t>Developer, Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Developer, Administrator, Miss Dina Nasr</t>
+          <t>Developer, Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Developer, Administrator, Miss Dina Nasr</t>
+          <t>Developer, Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Developer, Administrator, Miss Dina Nasr</t>
+          <t>Developer, Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Developer, Administrator, Miss Dina Nasr</t>
+          <t>Developer, Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Developer, Administrator, Miss Dina Nasr</t>
+          <t>Developer, Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Developer, Administrator, Miss Dina Nasr</t>
+          <t>Developer, Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Developer, Administrator, Miss Dina Nasr</t>
+          <t>Developer, Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Developer, Administrator, Miss Dina Nasr</t>
+          <t>Developer, Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Developer, Administrator, Miss Dina Nasr</t>
+          <t>Developer, Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Developer, Administrator, Miss Dina Nasr</t>
+          <t>Developer, Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Developer, Miss Dina Nasr, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Developer, Miss Dina Nasr, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Developer, Miss Dina Nasr, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Developer, Miss Dina Nasr, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Developer, Miss Dina Nasr, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Developer, Miss Dina Nasr, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Developer, Miss Dina Nasr, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Developer, Miss Dina Nasr, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Developer, Miss Dina Nasr, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Developer, Miss Dina Nasr, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Developer, Miss Dina Nasr, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Developer, Miss Dina Nasr, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Developer, Miss Dina Nasr, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Developer, Miss Dina Nasr, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Developer, Miss Dina Nasr, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Developer, Miss Dina Nasr, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Developer, Miss Dina Nasr, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Developer, Miss Dina Nasr, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Developer, Miss Dina Nasr, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Developer, Miss Dina Nasr, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Developer, Miss Dina Nasr, Administrator</t>
+          <t>Miss Dina Nasr, Administrator, Developer</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B2_session_analysis.xlsx
@@ -479,7 +479,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6793,7 +6793,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator, Developer</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
